--- a/data/trans_camb/IP18A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,17; -0,61</t>
+          <t>-20,56; -0,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 10,47</t>
+          <t>-12,01; 9,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 0,62</t>
+          <t>-23,58; 1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 14,87</t>
+          <t>-5,45; 14,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 11,2</t>
+          <t>-6,27; 11,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 23,12</t>
+          <t>-12,58; 23,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 4,87</t>
+          <t>-9,58; 4,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 7,42</t>
+          <t>-7,42; 6,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 5,64</t>
+          <t>-15,28; 4,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,96; -1,42</t>
+          <t>-65,97; -0,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 50,69</t>
+          <t>-39,96; 42,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,82; 14,91</t>
+          <t>-85,61; 4,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 111,23</t>
+          <t>-23,67; 112,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 89,55</t>
+          <t>-30,18; 85,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 165,2</t>
+          <t>-60,32; 160,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 26,64</t>
+          <t>-39,04; 25,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 40,27</t>
+          <t>-30,23; 35,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,52; 31,96</t>
+          <t>-65,62; 26,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 7,33</t>
+          <t>-13,31; 7,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 5,66</t>
+          <t>-14,12; 6,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 21,55</t>
+          <t>-19,95; 21,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 7,97</t>
+          <t>-13,33; 8,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 8,85</t>
+          <t>-11,84; 8,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 20,75</t>
+          <t>-22,33; 18,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 4,61</t>
+          <t>-10,75; 4,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 5,02</t>
+          <t>-10,38; 4,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 13,04</t>
+          <t>-17,92; 12,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 41,89</t>
+          <t>-44,42; 40,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 33,2</t>
+          <t>-47,02; 35,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,23; 100,82</t>
+          <t>-77,09; 117,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 44,01</t>
+          <t>-44,27; 43,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 48,42</t>
+          <t>-38,52; 54,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,56; 109,51</t>
+          <t>-82,23; 86,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 23,7</t>
+          <t>-37,07; 22,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 23,81</t>
+          <t>-36,81; 25,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 64,62</t>
+          <t>-70,33; 60,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 4,43</t>
+          <t>-16,82; 5,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 8,87</t>
+          <t>-14,24; 10,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 36,02</t>
+          <t>-26,29; 35,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 2,01</t>
+          <t>-16,81; 2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 12,68</t>
+          <t>-8,14; 13,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 40,02</t>
+          <t>-9,17; 36,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 1,47</t>
+          <t>-13,6; 0,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 7,76</t>
+          <t>-8,51; 7,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 28,91</t>
+          <t>-9,86; 29,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 28,97</t>
+          <t>-57,52; 33,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 55,33</t>
+          <t>-51,33; 68,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,64</t>
+          <t>-100,0; 182,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 17,0</t>
+          <t>-65,51; 20,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 79,71</t>
+          <t>-35,64; 89,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 248,93</t>
+          <t>-39,53; 224,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 10,24</t>
+          <t>-52,95; 3,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 45,24</t>
+          <t>-33,8; 46,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 158,84</t>
+          <t>-47,24; 147,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 3,75</t>
+          <t>-9,83; 4,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,97; -1,59</t>
+          <t>-15,16; -2,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 10,5</t>
+          <t>-17,6; 9,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 7,2</t>
+          <t>-7,11; 6,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 1,55</t>
+          <t>-12,24; 1,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 10,2</t>
+          <t>-12,38; 10,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 3,67</t>
+          <t>-6,04; 3,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,92; -2,14</t>
+          <t>-12,17; -2,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 5,75</t>
+          <t>-12,69; 4,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 17,64</t>
+          <t>-32,85; 22,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,34; -6,53</t>
+          <t>-50,96; -8,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 48,19</t>
+          <t>-62,87; 41,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 40,95</t>
+          <t>-28,09; 34,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 9,29</t>
+          <t>-47,58; 8,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 51,04</t>
+          <t>-50,87; 55,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 17,97</t>
+          <t>-23,4; 17,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,27; -10,34</t>
+          <t>-44,69; -12,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 26,68</t>
+          <t>-49,63; 20,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 7,77</t>
+          <t>-10,75; 8,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 3,07</t>
+          <t>-15,77; 2,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 21,3</t>
+          <t>-14,94; 22,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 7,01</t>
+          <t>-8,95; 6,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 10,95</t>
+          <t>-5,16; 10,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 11,44</t>
+          <t>-11,26; 12,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 5,9</t>
+          <t>-6,05; 5,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 5,23</t>
+          <t>-6,74; 4,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 9,83</t>
+          <t>-9,43; 9,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 45,65</t>
+          <t>-37,41; 51,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 17,14</t>
+          <t>-53,22; 16,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 108,61</t>
+          <t>-58,17; 124,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 66,12</t>
+          <t>-44,84; 60,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 98,11</t>
+          <t>-28,53; 94,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 94,4</t>
+          <t>-61,34; 107,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 39,05</t>
+          <t>-28,4; 35,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 35,05</t>
+          <t>-30,95; 31,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 60,42</t>
+          <t>-47,11; 56,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 20,46</t>
+          <t>-7,17; 19,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 14,48</t>
+          <t>-8,35; 15,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 23,62</t>
+          <t>-20,93; 23,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 11,48</t>
+          <t>-9,97; 11,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 16,46</t>
+          <t>-5,49; 17,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 20,44</t>
+          <t>-19,27; 22,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 10,88</t>
+          <t>-4,54; 10,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 12,23</t>
+          <t>-3,63; 13,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 9,8</t>
+          <t>-17,36; 12,36</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 137,08</t>
+          <t>-27,54; 128,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 100,69</t>
+          <t>-33,2; 107,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,08</t>
+          <t>-100,0; 143,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 87,78</t>
+          <t>-42,75; 97,8</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 137,08</t>
+          <t>-26,06; 146,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,83</t>
+          <t>-100,0; 160,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 68,59</t>
+          <t>-19,72; 70,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 79,03</t>
+          <t>-16,13; 86,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 58,45</t>
+          <t>-83,7; 77,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,94</t>
+          <t>-6,72; 1,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -0,73</t>
+          <t>-8,42; -0,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 2,04</t>
+          <t>-12,32; 1,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,55</t>
+          <t>-4,02; 3,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,39</t>
+          <t>-3,89; 3,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 5,93</t>
+          <t>-6,99; 5,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,97</t>
+          <t>-4,36; 0,94</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,42</t>
+          <t>-5,07; 0,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 1,59</t>
+          <t>-8,09; 1,24</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 4,21</t>
+          <t>-25,76; 5,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -3,12</t>
+          <t>-31,59; -3,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 8,71</t>
+          <t>-48,93; 8,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 19,86</t>
+          <t>-18,5; 17,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 19,02</t>
+          <t>-17,69; 18,44</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 31,23</t>
+          <t>-32,51; 31,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 4,53</t>
+          <t>-18,81; 4,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 1,85</t>
+          <t>-21,78; 0,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 7,5</t>
+          <t>-35,46; 6,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -0,99</t>
+          <t>-20,5; 0,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 9,21</t>
+          <t>-11,04; 11,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 1,01</t>
+          <t>-24,65; 1,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 14,28</t>
+          <t>-6,06; 14,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 11,24</t>
+          <t>-6,86; 10,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 23,52</t>
+          <t>-11,0; 23,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 4,34</t>
+          <t>-9,52; 4,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 6,58</t>
+          <t>-6,75; 7,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 4,73</t>
+          <t>-14,96; 5,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,97; -0,7</t>
+          <t>-66,88; 1,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 42,4</t>
+          <t>-37,79; 58,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 4,21</t>
+          <t>-84,94; 12,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 112,28</t>
+          <t>-27,85; 109,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 85,62</t>
+          <t>-31,93; 89,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 160,97</t>
+          <t>-56,33; 173,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 25,26</t>
+          <t>-38,89; 23,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 35,69</t>
+          <t>-26,42; 42,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 26,98</t>
+          <t>-64,72; 34,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 7,09</t>
+          <t>-13,52; 7,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 6,87</t>
+          <t>-13,93; 5,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 21,53</t>
+          <t>-21,09; 24,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 8,01</t>
+          <t>-12,74; 8,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 8,96</t>
+          <t>-12,45; 8,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 18,83</t>
+          <t>-22,17; 18,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 4,79</t>
+          <t>-10,41; 4,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 4,97</t>
+          <t>-9,67; 5,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 12,56</t>
+          <t>-17,0; 14,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 40,48</t>
+          <t>-45,62; 43,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,02; 35,4</t>
+          <t>-47,62; 31,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,09; 117,99</t>
+          <t>-76,68; 118,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 43,58</t>
+          <t>-43,1; 47,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 54,02</t>
+          <t>-41,2; 45,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,23; 86,43</t>
+          <t>-84,34; 90,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 22,91</t>
+          <t>-36,36; 24,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 25,18</t>
+          <t>-33,82; 26,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,33; 60,74</t>
+          <t>-67,77; 66,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 5,17</t>
+          <t>-16,39; 6,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 10,48</t>
+          <t>-15,07; 9,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 35,55</t>
+          <t>-26,45; 44,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 2,41</t>
+          <t>-15,84; 2,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 13,95</t>
+          <t>-8,25; 13,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 36,68</t>
+          <t>-10,08; 38,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 0,41</t>
+          <t>-13,2; 0,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 7,92</t>
+          <t>-9,07; 8,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 29,45</t>
+          <t>-9,73; 30,55</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 33,6</t>
+          <t>-58,82; 40,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 68,73</t>
+          <t>-53,78; 61,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,99</t>
+          <t>-100,0; 248,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 20,08</t>
+          <t>-65,31; 22,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 89,25</t>
+          <t>-33,67; 90,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 224,49</t>
+          <t>-43,81; 232,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 3,02</t>
+          <t>-52,24; 4,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 46,1</t>
+          <t>-35,64; 48,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 147,74</t>
+          <t>-43,85; 160,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 4,66</t>
+          <t>-10,1; 4,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -2,06</t>
+          <t>-15,84; -2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 9,44</t>
+          <t>-16,99; 10,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 6,26</t>
+          <t>-6,6; 6,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 1,15</t>
+          <t>-12,15; 0,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 10,54</t>
+          <t>-11,48; 10,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 3,61</t>
+          <t>-6,16; 3,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,17; -2,88</t>
+          <t>-12,15; -2,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 4,85</t>
+          <t>-12,24; 5,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 22,63</t>
+          <t>-34,42; 20,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,96; -8,79</t>
+          <t>-51,65; -8,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,87; 41,92</t>
+          <t>-61,5; 46,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 34,8</t>
+          <t>-25,06; 34,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 8,59</t>
+          <t>-47,07; 2,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 55,46</t>
+          <t>-49,04; 61,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 17,0</t>
+          <t>-24,28; 17,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,69; -12,97</t>
+          <t>-45,78; -11,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 20,57</t>
+          <t>-48,3; 23,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 8,35</t>
+          <t>-10,56; 7,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 2,64</t>
+          <t>-14,68; 3,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 22,48</t>
+          <t>-14,69; 21,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 6,93</t>
+          <t>-8,61; 7,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 10,63</t>
+          <t>-4,64; 11,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 12,01</t>
+          <t>-10,62; 11,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 5,12</t>
+          <t>-5,89; 6,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 4,85</t>
+          <t>-7,82; 4,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 9,17</t>
+          <t>-9,75; 8,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 51,24</t>
+          <t>-36,9; 44,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 16,5</t>
+          <t>-53,23; 18,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 124,22</t>
+          <t>-58,23; 114,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 60,5</t>
+          <t>-43,26; 74,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 94,16</t>
+          <t>-25,57; 108,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 107,96</t>
+          <t>-59,86; 98,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 35,25</t>
+          <t>-28,52; 42,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 31,13</t>
+          <t>-34,97; 33,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 56,45</t>
+          <t>-48,23; 57,54</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 19,24</t>
+          <t>-6,85; 19,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 15,73</t>
+          <t>-9,41; 15,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 23,6</t>
+          <t>-22,01; 22,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 11,4</t>
+          <t>-9,44; 10,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 17,8</t>
+          <t>-7,09; 15,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 22,39</t>
+          <t>-19,47; 19,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 10,98</t>
+          <t>-5,43; 10,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 13,24</t>
+          <t>-3,72; 12,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 12,36</t>
+          <t>-16,05; 11,75</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 128,92</t>
+          <t>-30,2; 120,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 107,82</t>
+          <t>-39,98; 101,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,19</t>
+          <t>-100,0; 145,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 97,8</t>
+          <t>-41,07; 89,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 146,16</t>
+          <t>-32,67; 132,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,84</t>
+          <t>-100,0; 152,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 70,36</t>
+          <t>-24,37; 65,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 86,16</t>
+          <t>-16,3; 78,35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,7; 77,09</t>
+          <t>-79,32; 77,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,06</t>
+          <t>-7,04; 0,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -0,71</t>
+          <t>-8,02; -0,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 1,87</t>
+          <t>-12,46; 1,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,02</t>
+          <t>-4,48; 3,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,24</t>
+          <t>-4,23; 3,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 5,79</t>
+          <t>-7,61; 5,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,94</t>
+          <t>-4,37; 0,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 0,13</t>
+          <t>-5,28; 0,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 1,24</t>
+          <t>-8,08; 1,22</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 5,08</t>
+          <t>-26,78; 2,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,59; -3,15</t>
+          <t>-31,26; -2,66</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 8,72</t>
+          <t>-49,42; 9,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 17,56</t>
+          <t>-20,34; 16,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 18,44</t>
+          <t>-19,33; 17,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 31,59</t>
+          <t>-37,05; 30,67</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 4,79</t>
+          <t>-18,83; 4,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 0,62</t>
+          <t>-22,47; 2,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 6,6</t>
+          <t>-35,07; 6,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-10,75</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,75</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-14,2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>-13,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>-5,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 0,06</t>
+          <t>-5,19; 14,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 11,37</t>
+          <t>-6,61; 11,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 1,12</t>
+          <t>-10,29; 25,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 14,36</t>
+          <t>-20,17; -0,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 10,96</t>
+          <t>-11,4; 10,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 23,38</t>
+          <t>-24,3; 4,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 4,33</t>
+          <t>-9,19; 4,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 7,67</t>
+          <t>-5,9; 7,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 5,67</t>
+          <t>-15,24; 7,97</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-42,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-2,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-56,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>-52,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-23,94%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 1,27</t>
+          <t>-26,18; 111,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 58,2</t>
+          <t>-30,96; 89,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-84,94; 12,05</t>
+          <t>-53,11; 179,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 109,91</t>
+          <t>-66,96; -1,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 89,71</t>
+          <t>-38,86; 50,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,33; 173,9</t>
+          <t>-84,14; 32,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 23,87</t>
+          <t>-37,67; 26,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 42,98</t>
+          <t>-24,52; 40,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,72; 34,46</t>
+          <t>-66,83; 39,95</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,39</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,43</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,39</t>
+          <t>-4,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 7,73</t>
+          <t>-13,31; 7,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 5,84</t>
+          <t>-13,15; 8,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 24,25</t>
+          <t>-22,71; 23,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 8,95</t>
+          <t>-13,09; 7,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 8,9</t>
+          <t>-13,93; 5,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 18,39</t>
+          <t>-22,34; 22,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 4,82</t>
+          <t>-10,55; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 5,33</t>
+          <t>-9,77; 5,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 14,97</t>
+          <t>-17,98; 14,99</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-9,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-5,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-21,83%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-12,54%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-14,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-17,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,73%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,89%</t>
+          <t>-15,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,29%</t>
+          <t>-18,92%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 43,96</t>
+          <t>-44,73; 44,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 31,4</t>
+          <t>-42,5; 48,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,68; 118,2</t>
+          <t>-85,43; 120,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 47,86</t>
+          <t>-45,53; 41,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 45,77</t>
+          <t>-45,19; 33,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 90,03</t>
+          <t>-80,81; 107,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 24,28</t>
+          <t>-37,23; 23,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 26,24</t>
+          <t>-34,48; 23,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 66,88</t>
+          <t>-69,49; 70,48</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10,37</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-5,21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,69</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-7,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,61</t>
+          <t>-8,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 6,02</t>
+          <t>-16,38; 2,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 9,61</t>
+          <t>-8,05; 12,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 44,19</t>
+          <t>-9,73; 41,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 2,58</t>
+          <t>-17,59; 4,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 13,7</t>
+          <t>-15,75; 8,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 38,54</t>
+          <t>-26,43; 33,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 0,56</t>
+          <t>-12,33; 1,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 8,16</t>
+          <t>-7,84; 7,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 30,55</t>
+          <t>-11,02; 29,35</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-35,92%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51,53%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-23,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-12,03%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-32,11%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-35,92%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>-38,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 40,05</t>
+          <t>-67,87; 17,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,78; 61,22</t>
+          <t>-34,19; 79,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 248,38</t>
+          <t>-47,29; 258,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 22,1</t>
+          <t>-56,69; 28,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 90,71</t>
+          <t>-55,98; 55,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 232,2</t>
+          <t>-100,0; 192,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,24; 4,83</t>
+          <t>-50,39; 10,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 48,93</t>
+          <t>-31,7; 45,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 160,12</t>
+          <t>-52,52; 160,71</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,69</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,92</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-8,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,69</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-2,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 4,5</t>
+          <t>-6,22; 7,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,84; -2,15</t>
+          <t>-11,76; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 10,83</t>
+          <t>-12,47; 10,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 6,4</t>
+          <t>-10,58; 3,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 0,31</t>
+          <t>-14,97; -1,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 10,43</t>
+          <t>-13,67; 14,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,63</t>
+          <t>-6,36; 3,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -2,41</t>
+          <t>-11,92; -2,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 5,01</t>
+          <t>-10,78; 7,38</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-25,85%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-9,75%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-11,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-32,71%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-20,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-25,85%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,2%</t>
+          <t>-10,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,87%</t>
+          <t>-11,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 20,05</t>
+          <t>-24,61; 40,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,65; -8,74</t>
+          <t>-47,14; 9,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 46,01</t>
+          <t>-54,48; 56,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 34,42</t>
+          <t>-34,24; 17,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 2,99</t>
+          <t>-50,34; -6,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 61,03</t>
+          <t>-50,83; 61,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 17,71</t>
+          <t>-23,75; 17,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,78; -11,09</t>
+          <t>-44,27; -10,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 23,38</t>
+          <t>-42,3; 35,42</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,31</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-5,96</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 7,62</t>
+          <t>-8,79; 7,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 3,28</t>
+          <t>-5,52; 10,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 21,26</t>
+          <t>-10,03; 12,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 7,5</t>
+          <t>-10,67; 7,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 11,64</t>
+          <t>-15,68; 3,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 11,8</t>
+          <t>-14,71; 21,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 6,0</t>
+          <t>-6,63; 5,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 4,83</t>
+          <t>-6,87; 5,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 8,8</t>
+          <t>-9,95; 10,51</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-2,94%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-5,37%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-5,76%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-26,28%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-1,64%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-2,94%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>19,92%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,85%</t>
+          <t>-0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,7%</t>
+          <t>-4,1%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 44,79</t>
+          <t>-46,09; 66,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 18,78</t>
+          <t>-28,08; 98,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 114,4</t>
+          <t>-59,84; 100,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 74,25</t>
+          <t>-38,25; 45,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 108,22</t>
+          <t>-55,71; 17,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 98,92</t>
+          <t>-61,13; 121,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 42,04</t>
+          <t>-30,42; 39,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 33,76</t>
+          <t>-32,09; 35,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 57,54</t>
+          <t>-48,14; 65,81</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-4,13</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>6,39</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>3,19</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-5,04</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,28</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,34</t>
+          <t>-4,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 19,25</t>
+          <t>-9,38; 11,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 15,5</t>
+          <t>-6,39; 16,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 22,12</t>
+          <t>-18,79; 24,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 10,79</t>
+          <t>-4,78; 20,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 15,99</t>
+          <t>-8,53; 14,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 19,92</t>
+          <t>-20,9; 23,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 10,7</t>
+          <t>-5,47; 10,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 12,05</t>
+          <t>-4,15; 12,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 11,75</t>
+          <t>-16,21; 12,31</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-23,08%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>31,1%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>15,54%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-24,52%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-29,5%</t>
+          <t>-25,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-27,75%</t>
+          <t>-24,83%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 120,86</t>
+          <t>-40,43; 87,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 101,94</t>
+          <t>-29,35; 137,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,34</t>
+          <t>-100,0; 191,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 89,79</t>
+          <t>-20,14; 137,08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 132,48</t>
+          <t>-34,34; 100,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,24</t>
+          <t>-100,0; 172,66</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 65,43</t>
+          <t>-24,28; 68,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 78,35</t>
+          <t>-18,93; 79,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 77,47</t>
+          <t>-79,03; 67,95</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,52</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-3,14</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,57</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-6,17</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-4,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-2,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 0,66</t>
+          <t>-4,12; 3,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -0,54</t>
+          <t>-3,92; 3,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 1,76</t>
+          <t>-6,68; 6,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,01</t>
+          <t>-7,05; 0,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 3,15</t>
+          <t>-8,39; -0,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 5,6</t>
+          <t>-11,34; 3,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,88</t>
+          <t>-4,16; 0,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,45</t>
+          <t>-4,72; 0,42</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 1,22</t>
+          <t>-7,26; 2,61</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-2,64%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-1,44%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-3,34%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-13,08%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-19,06%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-25,69%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-2,64%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-1,44%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-5,33%</t>
+          <t>-20,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-16,0%</t>
+          <t>-12,59%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 2,95</t>
+          <t>-18,91; 19,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,26; -2,66</t>
+          <t>-18,45; 19,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 9,52</t>
+          <t>-32,1; 36,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 16,67</t>
+          <t>-26,92; 4,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 17,94</t>
+          <t>-32,03; -3,12</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 30,67</t>
+          <t>-45,89; 16,39</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 4,54</t>
+          <t>-18,23; 4,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 2,15</t>
+          <t>-20,86; 1,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 6,32</t>
+          <t>-31,88; 12,61</t>
         </is>
       </c>
     </row>
